--- a/fast repo/MOLNAR_final.xlsx
+++ b/fast repo/MOLNAR_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f1231a3f872ac4c/Documents/github/skola/fast repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1F951CDE3C20957665BA6D9F5FDDA9DDF794F90F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C5645B-B43B-4A3D-85C0-85AA6583BBF1}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_1F951CDE3C20957665BA6D9F5FDDA9DDF794F90F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E49BD389-0F6F-4B79-8627-B34E9C8CDA0E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,9 +242,6 @@
     <t>Priemerny VSP celeho kruzku</t>
   </si>
   <si>
-    <t xml:space="preserve">ULOHA 5 - grafy </t>
-  </si>
-  <si>
     <t>Student</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
     <t>Priemerne znamky studentov</t>
   </si>
   <si>
-    <t xml:space="preserve">ULOHA 7 </t>
-  </si>
-  <si>
     <t>Kalendarny rad</t>
   </si>
   <si>
@@ -393,6 +387,12 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>ULOHA 7</t>
+  </si>
+  <si>
+    <t>ULOHA 5</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,8 +511,14 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,11 +642,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
       </patternFill>
     </fill>
     <fill>
@@ -927,17 +928,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="21"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="21"/>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="21"/>
     <xf numFmtId="0" fontId="16" fillId="23" borderId="21"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="21"/>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="21"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1108,16 +1108,16 @@
     <xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="25" borderId="14" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="24" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="25" borderId="14" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="24" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="14" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="14" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="25" borderId="14" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="24" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1"/>
@@ -1131,18 +1131,32 @@
     <xf numFmtId="2" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="21" xfId="6" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="24" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="23" borderId="14" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1151,37 +1165,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="25" borderId="14" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="40% - Accent4" xfId="7" builtinId="43"/>
+  <cellStyles count="7">
+    <cellStyle name="40% - Accent4" xfId="6" builtinId="43"/>
     <cellStyle name="60% - Accent1" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="60% - Accent2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Accent1" xfId="6" builtinId="29"/>
     <cellStyle name="Accent2" xfId="4" builtinId="33"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Neutral" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2409,6 +2401,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2673,62 +2669,62 @@
       </c>
     </row>
     <row r="2" spans="2:39" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="74"/>
-      <c r="Z2" s="74"/>
-      <c r="AA2" s="74"/>
+      <c r="B2" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+      <c r="AA2" s="72"/>
     </row>
     <row r="3" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="91"/>
-      <c r="T3" s="91"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="91"/>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="91"/>
-      <c r="Z3" s="91"/>
-      <c r="AA3" s="91"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
       <c r="AB3" s="46"/>
       <c r="AC3" s="46"/>
       <c r="AD3" s="46"/>
@@ -2756,39 +2752,39 @@
       <c r="F4" s="31">
         <v>6</v>
       </c>
-      <c r="G4" s="71" t="s">
+      <c r="G4" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="72"/>
+      <c r="H4" s="75"/>
       <c r="I4" s="32">
         <v>7</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="72"/>
+      <c r="K4" s="75"/>
       <c r="L4" s="32">
         <v>6</v>
       </c>
-      <c r="M4" s="71" t="s">
+      <c r="M4" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="72"/>
+      <c r="N4" s="75"/>
       <c r="O4" s="31">
         <v>7</v>
       </c>
-      <c r="P4" s="71" t="s">
+      <c r="P4" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="72"/>
+      <c r="Q4" s="75"/>
       <c r="R4" s="32">
         <v>6</v>
       </c>
-      <c r="S4" s="71" t="s">
+      <c r="S4" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="86"/>
-      <c r="U4" s="72"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="75"/>
       <c r="V4" s="4" t="s">
         <v>10</v>
       </c>
@@ -4458,10 +4454,10 @@
       <c r="G25" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="79" t="s">
+      <c r="H25" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="I25" s="80"/>
+      <c r="I25" s="86"/>
     </row>
     <row r="26" spans="2:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="23" t="s">
@@ -4487,11 +4483,11 @@
         <f>AVERAGE(P6:P23)</f>
         <v>2.6944444444444446</v>
       </c>
-      <c r="H26" s="88">
+      <c r="H26" s="76">
         <f>AVERAGE(S6:S23)</f>
         <v>2.3611111111111112</v>
       </c>
-      <c r="I26" s="76"/>
+      <c r="I26" s="77"/>
     </row>
     <row r="27" spans="2:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="23" t="s">
@@ -4517,11 +4513,11 @@
         <f>AVERAGE(Q6:Q23)</f>
         <v>1.7777777777777777</v>
       </c>
-      <c r="H27" s="88">
+      <c r="H27" s="76">
         <f>AVERAGE(T6:T23)</f>
         <v>1.9444444444444444</v>
       </c>
-      <c r="I27" s="76"/>
+      <c r="I27" s="77"/>
     </row>
     <row r="28" spans="2:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="2:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4537,37 +4533,37 @@
       <c r="B30" s="46"/>
     </row>
     <row r="31" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="H31" s="87" t="s">
-        <v>69</v>
-      </c>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="Z31" s="74"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="74"/>
-      <c r="AC31" s="74"/>
-      <c r="AD31" s="74"/>
-      <c r="AE31" s="74"/>
-      <c r="AF31" s="74"/>
+      <c r="H31" s="80" t="s">
+        <v>119</v>
+      </c>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="72"/>
+      <c r="S31" s="72"/>
+      <c r="T31" s="72"/>
+      <c r="U31" s="72"/>
+      <c r="V31" s="72"/>
+      <c r="W31" s="72"/>
+      <c r="X31" s="72"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
+      <c r="AA31" s="72"/>
+      <c r="AB31" s="72"/>
+      <c r="AC31" s="72"/>
+      <c r="AD31" s="72"/>
+      <c r="AE31" s="72"/>
+      <c r="AF31" s="72"/>
     </row>
     <row r="32" spans="2:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>13</v>
@@ -4905,39 +4901,42 @@
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.3">
       <c r="X64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="2:17" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="78" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="2:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="81" t="s">
+      <c r="C75" s="72"/>
+      <c r="D75" s="72"/>
+      <c r="E75" s="72"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="72"/>
+      <c r="I75" s="72"/>
+      <c r="J75" s="72"/>
+      <c r="K75" s="72"/>
+      <c r="L75" s="72"/>
+      <c r="M75" s="72"/>
+      <c r="N75" s="72"/>
+      <c r="O75" s="72"/>
+      <c r="P75" s="72"/>
+      <c r="Q75" s="72"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B76" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C75" s="82"/>
-      <c r="D75" s="82"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="47"/>
-      <c r="K75" s="47"/>
-      <c r="L75" s="47"/>
-      <c r="M75" s="47"/>
-      <c r="N75" s="47"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B76" s="54" t="s">
+      <c r="C76" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="54" t="s">
+      <c r="D76" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="D76" s="54" t="s">
+      <c r="E76" s="54" t="s">
         <v>75</v>
-      </c>
-      <c r="E76" s="54" t="s">
-        <v>76</v>
       </c>
       <c r="F76" s="47"/>
       <c r="G76" s="47"/>
@@ -4949,12 +4948,12 @@
       <c r="M76" s="47"/>
       <c r="N76" s="47"/>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B77" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77" s="55" t="s">
         <v>77</v>
-      </c>
-      <c r="C77" s="55" t="s">
-        <v>78</v>
       </c>
       <c r="D77" s="55" t="s">
         <v>10</v>
@@ -4973,15 +4972,15 @@
       <c r="M77" s="47"/>
       <c r="N77" s="47"/>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B78" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="55" t="s">
+      <c r="D78" s="55" t="s">
         <v>80</v>
-      </c>
-      <c r="D78" s="55" t="s">
-        <v>81</v>
       </c>
       <c r="E78" s="57">
         <f>MIN(Y6:Y23)</f>
@@ -4997,15 +4996,15 @@
       <c r="M78" s="47"/>
       <c r="N78" s="47"/>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B79" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="55" t="s">
+      <c r="D79" s="55" t="s">
         <v>83</v>
-      </c>
-      <c r="D79" s="55" t="s">
-        <v>84</v>
       </c>
       <c r="E79" s="57">
         <f>AVERAGE(W6:W23)</f>
@@ -5021,7 +5020,7 @@
       <c r="M79" s="47"/>
       <c r="N79" s="47"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F80" s="47"/>
       <c r="G80" s="47"/>
       <c r="H80" s="47"/>
@@ -5032,7 +5031,7 @@
       <c r="M80" s="47"/>
       <c r="N80" s="47"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F81" s="47"/>
       <c r="G81" s="47"/>
       <c r="H81" s="47"/>
@@ -5043,7 +5042,7 @@
       <c r="M81" s="47"/>
       <c r="N81" s="47"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B82" s="47"/>
       <c r="C82" s="47"/>
       <c r="D82" s="47"/>
@@ -5058,7 +5057,7 @@
       <c r="M82" s="47"/>
       <c r="N82" s="47"/>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="47"/>
       <c r="C83" s="47"/>
       <c r="D83" s="47"/>
@@ -5073,41 +5072,29 @@
       <c r="M83" s="47"/>
       <c r="N83" s="47"/>
     </row>
-    <row r="84" spans="2:14" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="C84" s="74"/>
-      <c r="D84" s="74"/>
-      <c r="E84" s="74"/>
-      <c r="F84" s="74"/>
-      <c r="G84" s="74"/>
-      <c r="H84" s="74"/>
-      <c r="I84" s="74"/>
-      <c r="J84" s="74"/>
-      <c r="K84" s="74"/>
-      <c r="L84" s="74"/>
-      <c r="M84" s="74"/>
-      <c r="N84" s="74"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B85" s="47"/>
-      <c r="C85" s="47"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="47"/>
-      <c r="K85" s="47"/>
-      <c r="L85" s="47"/>
-      <c r="M85" s="47"/>
-      <c r="N85" s="47"/>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="72"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="72"/>
+      <c r="P84" s="72"/>
+      <c r="Q84" s="72"/>
+    </row>
+    <row r="86" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B86" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C86" s="58">
         <f>DATE(2026,10,1)</f>
@@ -5158,7 +5145,7 @@
         <v>46307</v>
       </c>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B87" s="47"/>
       <c r="C87" s="47"/>
       <c r="D87" s="47"/>
@@ -5173,9 +5160,9 @@
       <c r="M87" s="47"/>
       <c r="N87" s="47"/>
     </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B88" s="60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C88" s="60"/>
       <c r="D88" s="47"/>
@@ -5190,9 +5177,9 @@
       <c r="M88" s="47"/>
       <c r="N88" s="47"/>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B89" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C89" s="59">
         <v>2</v>
@@ -5209,12 +5196,12 @@
       <c r="M89" s="47"/>
       <c r="N89" s="47"/>
     </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B90" s="48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C90" s="48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D90" s="47"/>
       <c r="E90" s="47"/>
@@ -5228,7 +5215,7 @@
       <c r="M90" s="47"/>
       <c r="N90" s="47"/>
     </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B91" s="17">
         <v>1</v>
       </c>
@@ -5247,7 +5234,7 @@
       <c r="M91" s="47"/>
       <c r="N91" s="47"/>
     </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B92" s="17">
         <f t="shared" ref="B92:B101" si="11">B91+1</f>
         <v>2</v>
@@ -5268,7 +5255,7 @@
       <c r="M92" s="47"/>
       <c r="N92" s="47"/>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B93" s="17">
         <f t="shared" si="11"/>
         <v>3</v>
@@ -5289,7 +5276,7 @@
       <c r="M93" s="47"/>
       <c r="N93" s="47"/>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B94" s="17">
         <f t="shared" si="11"/>
         <v>4</v>
@@ -5310,7 +5297,7 @@
       <c r="M94" s="47"/>
       <c r="N94" s="47"/>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B95" s="17">
         <f t="shared" si="11"/>
         <v>5</v>
@@ -5331,7 +5318,7 @@
       <c r="M95" s="47"/>
       <c r="N95" s="47"/>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B96" s="17">
         <f t="shared" si="11"/>
         <v>6</v>
@@ -5512,28 +5499,28 @@
       <c r="N105" s="47"/>
     </row>
     <row r="109" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B109" s="85" t="s">
-        <v>91</v>
-      </c>
-      <c r="C109" s="74"/>
-      <c r="D109" s="74"/>
-      <c r="E109" s="74"/>
-      <c r="F109" s="74"/>
-      <c r="G109" s="74"/>
-      <c r="H109" s="74"/>
-      <c r="I109" s="74"/>
-      <c r="J109" s="74"/>
-      <c r="K109" s="74"/>
-      <c r="L109" s="74"/>
-      <c r="M109" s="74"/>
-      <c r="N109" s="74"/>
-      <c r="O109" s="74"/>
-      <c r="P109" s="74"/>
-      <c r="Q109" s="74"/>
+      <c r="B109" s="78" t="s">
+        <v>89</v>
+      </c>
+      <c r="C109" s="72"/>
+      <c r="D109" s="72"/>
+      <c r="E109" s="72"/>
+      <c r="F109" s="72"/>
+      <c r="G109" s="72"/>
+      <c r="H109" s="72"/>
+      <c r="I109" s="72"/>
+      <c r="J109" s="72"/>
+      <c r="K109" s="72"/>
+      <c r="L109" s="72"/>
+      <c r="M109" s="72"/>
+      <c r="N109" s="72"/>
+      <c r="O109" s="72"/>
+      <c r="P109" s="72"/>
+      <c r="Q109" s="72"/>
     </row>
     <row r="111" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B111" s="49" t="s">
-        <v>92</v>
+      <c r="B111" s="88" t="s">
+        <v>90</v>
       </c>
       <c r="C111" s="50">
         <f>200/PI()</f>
@@ -5542,45 +5529,45 @@
     </row>
     <row r="113" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C113" s="61" t="s">
+        <v>92</v>
+      </c>
+      <c r="D113" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="C113" s="61" t="s">
+      <c r="E113" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="D113" s="61" t="s">
+      <c r="F113" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="E113" s="61" t="s">
+      <c r="G113" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="F113" s="61" t="s">
+      <c r="H113" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="G113" s="61" t="s">
+      <c r="I113" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="H113" s="61" t="s">
+      <c r="J113" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="I113" s="61" t="s">
+      <c r="K113" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="J113" s="61" t="s">
+      <c r="L113" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="K113" s="61" t="s">
+      <c r="M113" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="L113" s="61" t="s">
+      <c r="N113" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="M113" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="N113" s="75" t="s">
-        <v>105</v>
-      </c>
-      <c r="O113" s="76"/>
+      <c r="O113" s="77"/>
       <c r="P113" s="66"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.3">
@@ -5628,11 +5615,11 @@
         <f>IF(F114="ano",2*ATAN(I114/((C114+D114+E114)/2-E114))*$C$111,"-")</f>
         <v>31.191652150947728</v>
       </c>
-      <c r="N114" s="84">
+      <c r="N114" s="81">
         <f>IF(F114="ano",K114+L114+M114,"-")</f>
         <v>57.6108922390099</v>
       </c>
-      <c r="O114" s="76"/>
+      <c r="O114" s="77"/>
       <c r="P114" s="66"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.3">
@@ -5680,11 +5667,11 @@
         <f>IF(F115="ano",2*ATAN(I115/((C115+D115+E115)/2-E115))*$C$111,"-")</f>
         <v>31.180286528483915</v>
       </c>
-      <c r="N115" s="84">
+      <c r="N115" s="81">
         <f>IF(F115="ano",K115+L115+M115,"-")</f>
         <v>57.582327444935274</v>
       </c>
-      <c r="O115" s="76"/>
+      <c r="O115" s="77"/>
       <c r="P115" s="66"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.3">
@@ -5732,11 +5719,11 @@
         <f>IF(F116="ano",2*ATAN(I116/((C116+D116+E116)/2-E116))*$C$111,"-")</f>
         <v>4.7834155506761329</v>
       </c>
-      <c r="N116" s="84">
+      <c r="N116" s="81">
         <f>IF(F116="ano",K116+L116+M116,"-")</f>
         <v>59.301320874470051</v>
       </c>
-      <c r="O116" s="76"/>
+      <c r="O116" s="77"/>
       <c r="P116" s="66"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.3">
@@ -5784,11 +5771,11 @@
         <f>IF(F117="ano",2*ATAN(I117/((C117+D117+E117)/2-E117))*$C$111,"-")</f>
         <v>24.016273286753549</v>
       </c>
-      <c r="N117" s="84">
+      <c r="N117" s="81">
         <f>IF(F117="ano",K117+L117+M117,"-")</f>
         <v>55.366692240484468</v>
       </c>
-      <c r="O117" s="76"/>
+      <c r="O117" s="77"/>
       <c r="P117" s="66"/>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.3">
@@ -5836,11 +5823,11 @@
         <f>IF(F118="ano",2*ATAN(I118/((C118+D118+E118)/2-E118))*$C$111,"-")</f>
         <v>-</v>
       </c>
-      <c r="N118" s="84" t="str">
+      <c r="N118" s="81" t="str">
         <f>IF(F118="ano",K118+L118+M118,"-")</f>
         <v>-</v>
       </c>
-      <c r="O118" s="76"/>
+      <c r="O118" s="77"/>
       <c r="P118" s="66"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.3">
@@ -5851,24 +5838,24 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="51"/>
-      <c r="B122" s="85" t="s">
-        <v>106</v>
-      </c>
-      <c r="C122" s="74"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="74"/>
-      <c r="F122" s="74"/>
-      <c r="G122" s="74"/>
-      <c r="H122" s="74"/>
-      <c r="I122" s="74"/>
-      <c r="J122" s="74"/>
-      <c r="K122" s="74"/>
-      <c r="L122" s="74"/>
-      <c r="M122" s="74"/>
-      <c r="N122" s="74"/>
-      <c r="O122" s="74"/>
-      <c r="P122" s="74"/>
-      <c r="Q122" s="74"/>
+      <c r="B122" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="C122" s="72"/>
+      <c r="D122" s="72"/>
+      <c r="E122" s="72"/>
+      <c r="F122" s="72"/>
+      <c r="G122" s="72"/>
+      <c r="H122" s="72"/>
+      <c r="I122" s="72"/>
+      <c r="J122" s="72"/>
+      <c r="K122" s="72"/>
+      <c r="L122" s="72"/>
+      <c r="M122" s="72"/>
+      <c r="N122" s="72"/>
+      <c r="O122" s="72"/>
+      <c r="P122" s="72"/>
+      <c r="Q122" s="72"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="51"/>
@@ -5876,42 +5863,42 @@
     <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="51"/>
       <c r="B124" s="51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="51"/>
       <c r="B125" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B126" s="51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C128" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="D128" s="84"/>
+      <c r="E128" s="77"/>
+      <c r="G128" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I128" s="83" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="128" spans="1:17" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C128" s="89" t="s">
+      <c r="J128" s="84"/>
+      <c r="K128" s="77"/>
+      <c r="M128" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="D128" s="78"/>
-      <c r="E128" s="76"/>
-      <c r="G128" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="I128" s="77" t="s">
+      <c r="N128" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="J128" s="78"/>
-      <c r="K128" s="76"/>
-      <c r="M128" s="41" t="s">
+      <c r="P128" s="41" t="s">
         <v>112</v>
-      </c>
-      <c r="N128" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="P128" s="41" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="129" spans="3:16" x14ac:dyDescent="0.3">
@@ -5938,7 +5925,7 @@
         <v>-0.10000000000000009</v>
       </c>
       <c r="M129" s="44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N129" s="45">
         <f t="array" ref="N129:N131">MMULT(I129:K131,G129:G131)</f>
@@ -5972,7 +5959,7 @@
         <v>0.50000000000000011</v>
       </c>
       <c r="M130" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N130" s="45">
         <v>1</v>
@@ -6004,7 +5991,7 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="M131" s="44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N131" s="45">
         <v>-0.99999999999999956</v>
@@ -6014,11 +6001,11 @@
       </c>
     </row>
     <row r="133" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C133" s="77" t="s">
-        <v>118</v>
-      </c>
-      <c r="D133" s="78"/>
-      <c r="E133" s="76"/>
+      <c r="C133" s="83" t="s">
+        <v>116</v>
+      </c>
+      <c r="D133" s="84"/>
+      <c r="E133" s="77"/>
       <c r="G133" s="68">
         <f>MDETERM(C129:E131)</f>
         <v>-9.9999999999999982</v>
@@ -6030,7 +6017,7 @@
     </row>
     <row r="135" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G135" s="70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="3:16" x14ac:dyDescent="0.3">
@@ -6038,21 +6025,12 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B2:AA3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="H31:AF31"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="G4:H4"/>
     <mergeCell ref="N118:O118"/>
     <mergeCell ref="N114:O114"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="B84:N84"/>
     <mergeCell ref="N113:O113"/>
     <mergeCell ref="C133:E133"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="B75:E75"/>
     <mergeCell ref="N115:O115"/>
     <mergeCell ref="N117:O117"/>
     <mergeCell ref="B109:Q109"/>
@@ -6061,6 +6039,15 @@
     <mergeCell ref="B122:Q122"/>
     <mergeCell ref="N116:O116"/>
     <mergeCell ref="C128:E128"/>
+    <mergeCell ref="B2:AA3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="B84:Q84"/>
+    <mergeCell ref="B75:Q75"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="H31:AF31"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <conditionalFormatting sqref="Y6:Y23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
@@ -6073,9 +6060,10 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>